--- a/STRA_ORDER_BACKLOG_UPDATE/日次バッチ処理 資料.xlsx
+++ b/STRA_ORDER_BACKLOG_UPDATE/日次バッチ処理 資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\業務\ASTI受注データ抽出\Phase2\99_aska資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D8AF4C5-6EBD-4325-89C1-4E743112FEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6386CA3C-0C71-499D-A4E4-3F00C028BF5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{47029717-4381-40F4-8567-E9CC0CD3D37A}"/>
+    <workbookView xWindow="390" yWindow="0" windowWidth="25155" windowHeight="15480" xr2:uid="{47029717-4381-40F4-8567-E9CC0CD3D37A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>タスクスケジューラの自動化は、「トリガー」「条件」「操作」という3つの主要な要素で構成されています。</t>
   </si>
@@ -149,6 +149,32 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プログラムフォルダを指定すること</t>
+    <rPh sb="10" eb="12">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>空欄の場合 C:\Windows\System32 デフォルト設定となり ファイル書き出しでエラーとなる</t>
+    <rPh sb="0" eb="2">
+      <t>クウラン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="41" eb="42">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="43" eb="44">
+      <t>ダ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -157,7 +183,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +203,22 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -201,11 +243,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -361,50 +409,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>325900</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>234600</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF552F09-8B8C-7A90-2D75-83578761F162}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2062371" y="9607827"/>
-          <a:ext cx="5138095" cy="3357143"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>60</xdr:row>
@@ -430,7 +434,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -439,50 +443,6 @@
         <a:xfrm>
           <a:off x="6559826" y="14411739"/>
           <a:ext cx="3613334" cy="2600000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>277642</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>211673</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F33F5950-68F0-0E00-0106-9974D3DE4727}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7247283" y="17294087"/>
-          <a:ext cx="3027468" cy="3334216"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -671,6 +631,150 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>276840</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>210791</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E772E65-828F-8722-2D54-8EC57014C17B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7247283" y="17534283"/>
+          <a:ext cx="3026666" cy="3333334"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>16565</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>115956</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>679174</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>231913</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="11" name="直線矢印コネクタ 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D81F544-CC3E-F842-801B-512409F93693}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="10013674" y="18851217"/>
+          <a:ext cx="662609" cy="115957"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="C00000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>405111</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>195345</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B23D44B3-8557-8412-F581-D3E7D80BA86B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1747630" y="10328413"/>
+          <a:ext cx="6592220" cy="3558084"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -973,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEB60B91-F8C8-46AB-BD7F-FE25FE2D287A}">
-  <dimension ref="B1:E92"/>
+  <dimension ref="B1:Q92"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.875" customWidth="1"/>
@@ -1072,6 +1176,16 @@
         <v>9</v>
       </c>
     </row>
+    <row r="79" spans="17:17" x14ac:dyDescent="0.4">
+      <c r="Q79" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="17:17" x14ac:dyDescent="0.4">
+      <c r="Q80" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B89" t="s">
         <v>19</v>
